--- a/fix/slicing-type-this/ig/StructureDefinition-fr-cda-resultats-examens-de-biologie-medicale.xlsx
+++ b/fix/slicing-type-this/ig/StructureDefinition-fr-cda-resultats-examens-de-biologie-medicale.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T14:14:01+00:00</t>
+    <t>2026-10-06T20:02:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/slicing-type-this/ig/StructureDefinition-fr-cda-resultats-examens-de-biologie-medicale.xlsx
+++ b/fix/slicing-type-this/ig/StructureDefinition-fr-cda-resultats-examens-de-biologie-medicale.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T20:02:10+00:00</t>
+    <t>2026-10-07T08:37:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/slicing-type-this/ig/StructureDefinition-fr-cda-resultats-examens-de-biologie-medicale.xlsx
+++ b/fix/slicing-type-this/ig/StructureDefinition-fr-cda-resultats-examens-de-biologie-medicale.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T08:37:44+00:00</t>
+    <t>2026-10-07T09:51:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/slicing-type-this/ig/StructureDefinition-fr-cda-resultats-examens-de-biologie-medicale.xlsx
+++ b/fix/slicing-type-this/ig/StructureDefinition-fr-cda-resultats-examens-de-biologie-medicale.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9583" uniqueCount="644">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9586" uniqueCount="645">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T08:06:17+00:00</t>
+    <t>2026-10-08T10:07:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -897,10 +897,13 @@
     <t>Act.participant.typeCode</t>
   </si>
   <si>
+    <t>Code issu du JDV_HL7_v3_ParticipationType_CISIS (2.16.840.1.113883.1.11.10901).</t>
+  </si>
+  <si>
     <t>AUTHEN</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ParticipationType-cisis|20260916095457</t>
+    <t>http://hl7.org/cda/stds/core/ValueSet/CDAParticipationType|2.0.3-sd</t>
   </si>
   <si>
     <t>Participant2.typeCode</t>
@@ -2353,7 +2356,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="73.28515625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="72.671875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="60.20703125" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
@@ -9738,7 +9741,9 @@
       <c r="K73" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="L73" s="2"/>
+      <c r="L73" t="s" s="2">
+        <v>282</v>
+      </c>
       <c r="M73" s="2"/>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -9750,7 +9755,7 @@
         <v>75</v>
       </c>
       <c r="S73" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="T73" t="s" s="2">
         <v>75</v>
@@ -9769,7 +9774,7 @@
       </c>
       <c r="Y73" s="2"/>
       <c r="Z73" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>75</v>
@@ -9787,7 +9792,7 @@
         <v>75</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>76</v>
@@ -9807,10 +9812,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9844,7 +9849,7 @@
       </c>
       <c r="Q74" s="2"/>
       <c r="R74" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="S74" t="s" s="2">
         <v>75</v>
@@ -9866,7 +9871,7 @@
       </c>
       <c r="Y74" s="2"/>
       <c r="Z74" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>75</v>
@@ -9884,7 +9889,7 @@
         <v>75</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -9904,10 +9909,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9983,7 +9988,7 @@
         <v>75</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -10003,10 +10008,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10032,10 +10037,10 @@
         <v>212</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -10086,7 +10091,7 @@
         <v>75</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -10106,10 +10111,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10207,10 +10212,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10233,11 +10238,11 @@
         <v>75</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L78" s="2"/>
       <c r="M78" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -10288,7 +10293,7 @@
         <v>75</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -10308,10 +10313,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10338,12 +10343,12 @@
       </c>
       <c r="L79" s="2"/>
       <c r="M79" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q79" s="2"/>
       <c r="R79" t="s" s="2">
@@ -10369,7 +10374,7 @@
       </c>
       <c r="Y79" s="2"/>
       <c r="Z79" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>75</v>
@@ -10387,7 +10392,7 @@
         <v>75</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -10407,17 +10412,17 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E80" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F80" t="s" s="2">
         <v>81</v>
@@ -10435,11 +10440,11 @@
         <v>75</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L80" s="2"/>
       <c r="M80" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -10490,7 +10495,7 @@
         <v>75</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -10510,17 +10515,17 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E81" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F81" t="s" s="2">
         <v>81</v>
@@ -10538,11 +10543,11 @@
         <v>75</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L81" s="2"/>
       <c r="M81" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -10593,7 +10598,7 @@
         <v>75</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -10613,17 +10618,17 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E82" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F82" t="s" s="2">
         <v>81</v>
@@ -10641,11 +10646,11 @@
         <v>75</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L82" s="2"/>
       <c r="M82" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -10696,7 +10701,7 @@
         <v>75</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -10716,17 +10721,17 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E83" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F83" t="s" s="2">
         <v>81</v>
@@ -10744,11 +10749,11 @@
         <v>75</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L83" s="2"/>
       <c r="M83" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -10799,7 +10804,7 @@
         <v>75</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -10819,10 +10824,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10898,7 +10903,7 @@
         <v>75</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -10918,10 +10923,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10944,13 +10949,13 @@
         <v>75</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -11001,7 +11006,7 @@
         <v>75</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>76</v>
@@ -11021,13 +11026,13 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B86" t="s" s="2">
         <v>232</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D86" t="s" s="2">
         <v>75</v>
@@ -11052,10 +11057,10 @@
         <v>237</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -11126,7 +11131,7 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B87" t="s" s="2">
         <v>240</v>
@@ -11227,7 +11232,7 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B88" t="s" s="2">
         <v>242</v>
@@ -11328,7 +11333,7 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B89" t="s" s="2">
         <v>244</v>
@@ -11429,7 +11434,7 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B90" t="s" s="2">
         <v>246</v>
@@ -11530,7 +11535,7 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B91" t="s" s="2">
         <v>248</v>
@@ -11633,7 +11638,7 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B92" t="s" s="2">
         <v>250</v>
@@ -11736,7 +11741,7 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B93" t="s" s="2">
         <v>252</v>
@@ -11839,7 +11844,7 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B94" t="s" s="2">
         <v>254</v>
@@ -11942,7 +11947,7 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B95" t="s" s="2">
         <v>256</v>
@@ -12043,7 +12048,7 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B96" t="s" s="2">
         <v>262</v>
@@ -12144,7 +12149,7 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B97" t="s" s="2">
         <v>264</v>
@@ -12247,7 +12252,7 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B98" t="s" s="2">
         <v>266</v>
@@ -12350,7 +12355,7 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B99" t="s" s="2">
         <v>268</v>
@@ -12453,7 +12458,7 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B100" t="s" s="2">
         <v>271</v>
@@ -12556,7 +12561,7 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B101" t="s" s="2">
         <v>256</v>
@@ -12661,7 +12666,7 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B102" t="s" s="2">
         <v>262</v>
@@ -12762,7 +12767,7 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B103" t="s" s="2">
         <v>264</v>
@@ -12865,7 +12870,7 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B104" t="s" s="2">
         <v>266</v>
@@ -12968,7 +12973,7 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B105" t="s" s="2">
         <v>268</v>
@@ -13071,7 +13076,7 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B106" t="s" s="2">
         <v>271</v>
@@ -13174,7 +13179,7 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B107" t="s" s="2">
         <v>281</v>
@@ -13202,7 +13207,9 @@
       <c r="K107" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="L107" s="2"/>
+      <c r="L107" t="s" s="2">
+        <v>282</v>
+      </c>
       <c r="M107" s="2"/>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -13214,7 +13221,7 @@
         <v>75</v>
       </c>
       <c r="S107" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="T107" t="s" s="2">
         <v>75</v>
@@ -13233,7 +13240,7 @@
       </c>
       <c r="Y107" s="2"/>
       <c r="Z107" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>75</v>
@@ -13251,7 +13258,7 @@
         <v>75</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>76</v>
@@ -13271,10 +13278,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -13308,7 +13315,7 @@
       </c>
       <c r="Q108" s="2"/>
       <c r="R108" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="S108" t="s" s="2">
         <v>75</v>
@@ -13330,7 +13337,7 @@
       </c>
       <c r="Y108" s="2"/>
       <c r="Z108" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>75</v>
@@ -13348,7 +13355,7 @@
         <v>75</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>81</v>
@@ -13368,10 +13375,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13447,7 +13454,7 @@
         <v>75</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>81</v>
@@ -13467,10 +13474,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -13496,10 +13503,10 @@
         <v>212</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -13550,7 +13557,7 @@
         <v>75</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>81</v>
@@ -13570,10 +13577,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -13671,10 +13678,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -13697,11 +13704,11 @@
         <v>75</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L112" s="2"/>
       <c r="M112" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -13752,7 +13759,7 @@
         <v>75</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>81</v>
@@ -13772,10 +13779,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -13802,12 +13809,12 @@
       </c>
       <c r="L113" s="2"/>
       <c r="M113" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q113" s="2"/>
       <c r="R113" t="s" s="2">
@@ -13833,7 +13840,7 @@
       </c>
       <c r="Y113" s="2"/>
       <c r="Z113" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>75</v>
@@ -13851,7 +13858,7 @@
         <v>75</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>81</v>
@@ -13871,17 +13878,17 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E114" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F114" t="s" s="2">
         <v>81</v>
@@ -13899,11 +13906,11 @@
         <v>75</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L114" s="2"/>
       <c r="M114" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -13954,7 +13961,7 @@
         <v>75</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>81</v>
@@ -13974,17 +13981,17 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E115" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F115" t="s" s="2">
         <v>81</v>
@@ -14002,11 +14009,11 @@
         <v>75</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L115" s="2"/>
       <c r="M115" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -14057,7 +14064,7 @@
         <v>75</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>81</v>
@@ -14077,17 +14084,17 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E116" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F116" t="s" s="2">
         <v>81</v>
@@ -14105,11 +14112,11 @@
         <v>75</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L116" s="2"/>
       <c r="M116" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -14160,7 +14167,7 @@
         <v>75</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>81</v>
@@ -14180,17 +14187,17 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E117" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F117" t="s" s="2">
         <v>81</v>
@@ -14208,11 +14215,11 @@
         <v>75</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L117" s="2"/>
       <c r="M117" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -14263,7 +14270,7 @@
         <v>75</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>81</v>
@@ -14283,10 +14290,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -14362,7 +14369,7 @@
         <v>75</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>81</v>
@@ -14382,10 +14389,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -14408,13 +14415,13 @@
         <v>75</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -14465,7 +14472,7 @@
         <v>75</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>76</v>
@@ -14485,13 +14492,13 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B120" t="s" s="2">
         <v>232</v>
       </c>
       <c r="C120" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D120" t="s" s="2">
         <v>75</v>
@@ -14516,10 +14523,10 @@
         <v>237</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -14590,7 +14597,7 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B121" t="s" s="2">
         <v>240</v>
@@ -14691,7 +14698,7 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B122" t="s" s="2">
         <v>242</v>
@@ -14792,7 +14799,7 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B123" t="s" s="2">
         <v>244</v>
@@ -14893,7 +14900,7 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B124" t="s" s="2">
         <v>246</v>
@@ -14994,7 +15001,7 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B125" t="s" s="2">
         <v>248</v>
@@ -15097,7 +15104,7 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B126" t="s" s="2">
         <v>250</v>
@@ -15200,7 +15207,7 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B127" t="s" s="2">
         <v>252</v>
@@ -15303,7 +15310,7 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B128" t="s" s="2">
         <v>254</v>
@@ -15406,7 +15413,7 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B129" t="s" s="2">
         <v>256</v>
@@ -15507,7 +15514,7 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B130" t="s" s="2">
         <v>262</v>
@@ -15608,7 +15615,7 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B131" t="s" s="2">
         <v>264</v>
@@ -15711,7 +15718,7 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B132" t="s" s="2">
         <v>266</v>
@@ -15814,7 +15821,7 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B133" t="s" s="2">
         <v>268</v>
@@ -15917,7 +15924,7 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B134" t="s" s="2">
         <v>271</v>
@@ -16020,7 +16027,7 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B135" t="s" s="2">
         <v>256</v>
@@ -16125,7 +16132,7 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B136" t="s" s="2">
         <v>262</v>
@@ -16226,7 +16233,7 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B137" t="s" s="2">
         <v>264</v>
@@ -16329,7 +16336,7 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B138" t="s" s="2">
         <v>266</v>
@@ -16432,7 +16439,7 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B139" t="s" s="2">
         <v>268</v>
@@ -16535,7 +16542,7 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B140" t="s" s="2">
         <v>271</v>
@@ -16638,7 +16645,7 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B141" t="s" s="2">
         <v>281</v>
@@ -16666,7 +16673,9 @@
       <c r="K141" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="L141" s="2"/>
+      <c r="L141" t="s" s="2">
+        <v>282</v>
+      </c>
       <c r="M141" s="2"/>
       <c r="N141" s="2"/>
       <c r="O141" s="2"/>
@@ -16678,7 +16687,7 @@
         <v>75</v>
       </c>
       <c r="S141" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="T141" t="s" s="2">
         <v>75</v>
@@ -16697,7 +16706,7 @@
       </c>
       <c r="Y141" s="2"/>
       <c r="Z141" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AA141" t="s" s="2">
         <v>75</v>
@@ -16715,7 +16724,7 @@
         <v>75</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>76</v>
@@ -16735,10 +16744,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -16772,7 +16781,7 @@
       </c>
       <c r="Q142" s="2"/>
       <c r="R142" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="S142" t="s" s="2">
         <v>75</v>
@@ -16794,7 +16803,7 @@
       </c>
       <c r="Y142" s="2"/>
       <c r="Z142" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AA142" t="s" s="2">
         <v>75</v>
@@ -16812,7 +16821,7 @@
         <v>75</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>81</v>
@@ -16832,10 +16841,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -16911,7 +16920,7 @@
         <v>75</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>81</v>
@@ -16931,10 +16940,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -16960,10 +16969,10 @@
         <v>212</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N144" s="2"/>
       <c r="O144" s="2"/>
@@ -17014,7 +17023,7 @@
         <v>75</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>81</v>
@@ -17034,10 +17043,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -17135,10 +17144,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -17161,11 +17170,11 @@
         <v>75</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L146" s="2"/>
       <c r="M146" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" s="2"/>
@@ -17216,7 +17225,7 @@
         <v>75</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>81</v>
@@ -17236,10 +17245,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -17266,12 +17275,12 @@
       </c>
       <c r="L147" s="2"/>
       <c r="M147" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N147" s="2"/>
       <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q147" s="2"/>
       <c r="R147" t="s" s="2">
@@ -17297,7 +17306,7 @@
       </c>
       <c r="Y147" s="2"/>
       <c r="Z147" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AA147" t="s" s="2">
         <v>75</v>
@@ -17315,7 +17324,7 @@
         <v>75</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>81</v>
@@ -17335,17 +17344,17 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E148" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F148" t="s" s="2">
         <v>81</v>
@@ -17363,11 +17372,11 @@
         <v>75</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L148" s="2"/>
       <c r="M148" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" s="2"/>
@@ -17418,7 +17427,7 @@
         <v>75</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>81</v>
@@ -17438,17 +17447,17 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E149" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F149" t="s" s="2">
         <v>81</v>
@@ -17466,11 +17475,11 @@
         <v>75</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L149" s="2"/>
       <c r="M149" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N149" s="2"/>
       <c r="O149" s="2"/>
@@ -17521,7 +17530,7 @@
         <v>75</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>81</v>
@@ -17541,17 +17550,17 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E150" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F150" t="s" s="2">
         <v>81</v>
@@ -17569,11 +17578,11 @@
         <v>75</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L150" s="2"/>
       <c r="M150" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N150" s="2"/>
       <c r="O150" s="2"/>
@@ -17624,7 +17633,7 @@
         <v>75</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>81</v>
@@ -17644,17 +17653,17 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E151" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F151" t="s" s="2">
         <v>81</v>
@@ -17672,11 +17681,11 @@
         <v>75</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L151" s="2"/>
       <c r="M151" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N151" s="2"/>
       <c r="O151" s="2"/>
@@ -17727,7 +17736,7 @@
         <v>75</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>81</v>
@@ -17747,10 +17756,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -17826,7 +17835,7 @@
         <v>75</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>81</v>
@@ -17846,10 +17855,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -17872,13 +17881,13 @@
         <v>75</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N153" s="2"/>
       <c r="O153" s="2"/>
@@ -17929,7 +17938,7 @@
         <v>75</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>76</v>
@@ -17949,10 +17958,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -17975,7 +17984,7 @@
         <v>75</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="L154" s="2"/>
       <c r="M154" s="2"/>
@@ -18016,7 +18025,7 @@
         <v>75</v>
       </c>
       <c r="AB154" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AC154" s="2"/>
       <c r="AD154" t="s" s="2">
@@ -18026,7 +18035,7 @@
         <v>125</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>81</v>
@@ -18046,13 +18055,13 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C155" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D155" t="s" s="2">
         <v>75</v>
@@ -18074,7 +18083,7 @@
         <v>75</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="L155" s="2"/>
       <c r="M155" s="2"/>
@@ -18127,7 +18136,7 @@
         <v>75</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>81</v>
@@ -18147,10 +18156,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -18248,10 +18257,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -18349,10 +18358,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -18450,10 +18459,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -18551,10 +18560,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -18654,10 +18663,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -18757,10 +18766,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -18860,10 +18869,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -18963,10 +18972,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -19064,10 +19073,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -19104,7 +19113,7 @@
         <v>75</v>
       </c>
       <c r="S165" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="T165" t="s" s="2">
         <v>75</v>
@@ -19123,7 +19132,7 @@
       </c>
       <c r="Y165" s="2"/>
       <c r="Z165" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AA165" t="s" s="2">
         <v>75</v>
@@ -19141,7 +19150,7 @@
         <v>75</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>76</v>
@@ -19161,10 +19170,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -19191,7 +19200,7 @@
       </c>
       <c r="L166" s="2"/>
       <c r="M166" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" s="2"/>
@@ -19242,7 +19251,7 @@
         <v>75</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>81</v>
@@ -19262,10 +19271,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -19292,12 +19301,12 @@
       </c>
       <c r="L167" s="2"/>
       <c r="M167" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N167" s="2"/>
       <c r="O167" s="2"/>
       <c r="P167" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="Q167" s="2"/>
       <c r="R167" t="s" s="2">
@@ -19343,7 +19352,7 @@
         <v>75</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>81</v>
@@ -19363,10 +19372,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -19442,7 +19451,7 @@
         <v>75</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>81</v>
@@ -19462,10 +19471,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -19488,7 +19497,7 @@
         <v>75</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="L169" s="2"/>
       <c r="M169" s="2"/>
@@ -19541,7 +19550,7 @@
         <v>75</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>81</v>
@@ -19561,10 +19570,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -19587,7 +19596,7 @@
         <v>75</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="L170" s="2"/>
       <c r="M170" s="2"/>
@@ -19640,7 +19649,7 @@
         <v>75</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>81</v>
@@ -19660,10 +19669,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -19686,7 +19695,7 @@
         <v>75</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L171" s="2"/>
       <c r="M171" s="2"/>
@@ -19739,7 +19748,7 @@
         <v>75</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>81</v>
@@ -19759,10 +19768,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -19785,7 +19794,7 @@
         <v>75</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="L172" s="2"/>
       <c r="M172" s="2"/>
@@ -19838,7 +19847,7 @@
         <v>75</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>81</v>
@@ -19858,10 +19867,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -19884,7 +19893,7 @@
         <v>75</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="L173" s="2"/>
       <c r="M173" s="2"/>
@@ -19937,7 +19946,7 @@
         <v>75</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>81</v>
@@ -19957,10 +19966,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -19983,7 +19992,7 @@
         <v>75</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="L174" s="2"/>
       <c r="M174" s="2"/>
@@ -20036,7 +20045,7 @@
         <v>75</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>81</v>
@@ -20056,10 +20065,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -20082,7 +20091,7 @@
         <v>75</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="L175" s="2"/>
       <c r="M175" s="2"/>
@@ -20135,7 +20144,7 @@
         <v>75</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>81</v>
@@ -20155,10 +20164,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -20181,7 +20190,7 @@
         <v>75</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="L176" s="2"/>
       <c r="M176" s="2"/>
@@ -20234,7 +20243,7 @@
         <v>75</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>81</v>
@@ -20254,10 +20263,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -20280,7 +20289,7 @@
         <v>75</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="L177" s="2"/>
       <c r="M177" s="2"/>
@@ -20333,7 +20342,7 @@
         <v>75</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>81</v>
@@ -20353,10 +20362,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -20379,7 +20388,7 @@
         <v>75</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="L178" s="2"/>
       <c r="M178" s="2"/>
@@ -20432,7 +20441,7 @@
         <v>75</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>81</v>
@@ -20452,10 +20461,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -20478,7 +20487,7 @@
         <v>75</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="L179" s="2"/>
       <c r="M179" s="2"/>
@@ -20531,7 +20540,7 @@
         <v>75</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>81</v>
@@ -20551,13 +20560,13 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C180" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D180" t="s" s="2">
         <v>75</v>
@@ -20579,7 +20588,7 @@
         <v>75</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="L180" s="2"/>
       <c r="M180" s="2"/>
@@ -20632,7 +20641,7 @@
         <v>75</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>81</v>
@@ -20652,10 +20661,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -20753,10 +20762,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -20854,10 +20863,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -20955,10 +20964,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -21056,10 +21065,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -21159,10 +21168,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -21262,10 +21271,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -21365,10 +21374,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -21468,10 +21477,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -21569,10 +21578,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -21609,7 +21618,7 @@
         <v>75</v>
       </c>
       <c r="S190" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="T190" t="s" s="2">
         <v>75</v>
@@ -21628,7 +21637,7 @@
       </c>
       <c r="Y190" s="2"/>
       <c r="Z190" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AA190" t="s" s="2">
         <v>75</v>
@@ -21646,7 +21655,7 @@
         <v>75</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>76</v>
@@ -21666,10 +21675,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -21696,7 +21705,7 @@
       </c>
       <c r="L191" s="2"/>
       <c r="M191" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N191" s="2"/>
       <c r="O191" s="2"/>
@@ -21747,7 +21756,7 @@
         <v>75</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>81</v>
@@ -21767,10 +21776,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -21797,12 +21806,12 @@
       </c>
       <c r="L192" s="2"/>
       <c r="M192" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N192" s="2"/>
       <c r="O192" s="2"/>
       <c r="P192" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="Q192" s="2"/>
       <c r="R192" t="s" s="2">
@@ -21848,7 +21857,7 @@
         <v>75</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>81</v>
@@ -21868,10 +21877,10 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -21947,7 +21956,7 @@
         <v>75</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>81</v>
@@ -21967,10 +21976,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -21993,7 +22002,7 @@
         <v>75</v>
       </c>
       <c r="K194" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="L194" s="2"/>
       <c r="M194" s="2"/>
@@ -22046,7 +22055,7 @@
         <v>75</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>81</v>
@@ -22066,10 +22075,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -22092,7 +22101,7 @@
         <v>75</v>
       </c>
       <c r="K195" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="L195" s="2"/>
       <c r="M195" s="2"/>
@@ -22145,7 +22154,7 @@
         <v>75</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>81</v>
@@ -22165,10 +22174,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -22191,7 +22200,7 @@
         <v>75</v>
       </c>
       <c r="K196" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L196" s="2"/>
       <c r="M196" s="2"/>
@@ -22244,7 +22253,7 @@
         <v>75</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>81</v>
@@ -22264,10 +22273,10 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -22290,7 +22299,7 @@
         <v>75</v>
       </c>
       <c r="K197" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="L197" s="2"/>
       <c r="M197" s="2"/>
@@ -22343,7 +22352,7 @@
         <v>75</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>81</v>
@@ -22363,10 +22372,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -22389,7 +22398,7 @@
         <v>75</v>
       </c>
       <c r="K198" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="L198" s="2"/>
       <c r="M198" s="2"/>
@@ -22442,7 +22451,7 @@
         <v>75</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>81</v>
@@ -22462,10 +22471,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -22488,7 +22497,7 @@
         <v>75</v>
       </c>
       <c r="K199" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="L199" s="2"/>
       <c r="M199" s="2"/>
@@ -22541,7 +22550,7 @@
         <v>75</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>81</v>
@@ -22561,10 +22570,10 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -22587,7 +22596,7 @@
         <v>75</v>
       </c>
       <c r="K200" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="L200" s="2"/>
       <c r="M200" s="2"/>
@@ -22640,7 +22649,7 @@
         <v>75</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>81</v>
@@ -22660,10 +22669,10 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -22686,7 +22695,7 @@
         <v>75</v>
       </c>
       <c r="K201" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="L201" s="2"/>
       <c r="M201" s="2"/>
@@ -22739,7 +22748,7 @@
         <v>75</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>81</v>
@@ -22759,10 +22768,10 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -22785,7 +22794,7 @@
         <v>75</v>
       </c>
       <c r="K202" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="L202" s="2"/>
       <c r="M202" s="2"/>
@@ -22838,7 +22847,7 @@
         <v>75</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>81</v>
@@ -22858,10 +22867,10 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -22884,7 +22893,7 @@
         <v>75</v>
       </c>
       <c r="K203" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="L203" s="2"/>
       <c r="M203" s="2"/>
@@ -22937,7 +22946,7 @@
         <v>75</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>81</v>
@@ -22957,10 +22966,10 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -22983,7 +22992,7 @@
         <v>75</v>
       </c>
       <c r="K204" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="L204" s="2"/>
       <c r="M204" s="2"/>
@@ -23036,7 +23045,7 @@
         <v>75</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AG204" t="s" s="2">
         <v>81</v>
@@ -23056,13 +23065,13 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C205" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D205" t="s" s="2">
         <v>75</v>
@@ -23084,7 +23093,7 @@
         <v>75</v>
       </c>
       <c r="K205" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="L205" s="2"/>
       <c r="M205" s="2"/>
@@ -23137,7 +23146,7 @@
         <v>75</v>
       </c>
       <c r="AF205" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG205" t="s" s="2">
         <v>81</v>
@@ -23157,10 +23166,10 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -23258,10 +23267,10 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -23359,10 +23368,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -23460,10 +23469,10 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -23561,10 +23570,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -23664,10 +23673,10 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -23767,10 +23776,10 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -23870,10 +23879,10 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -23973,10 +23982,10 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -24074,10 +24083,10 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -24114,7 +24123,7 @@
         <v>75</v>
       </c>
       <c r="S215" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="T215" t="s" s="2">
         <v>75</v>
@@ -24133,7 +24142,7 @@
       </c>
       <c r="Y215" s="2"/>
       <c r="Z215" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AA215" t="s" s="2">
         <v>75</v>
@@ -24151,7 +24160,7 @@
         <v>75</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>76</v>
@@ -24171,10 +24180,10 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -24201,7 +24210,7 @@
       </c>
       <c r="L216" s="2"/>
       <c r="M216" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N216" s="2"/>
       <c r="O216" s="2"/>
@@ -24252,7 +24261,7 @@
         <v>75</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>81</v>
@@ -24272,10 +24281,10 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -24302,12 +24311,12 @@
       </c>
       <c r="L217" s="2"/>
       <c r="M217" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N217" s="2"/>
       <c r="O217" s="2"/>
       <c r="P217" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="Q217" s="2"/>
       <c r="R217" t="s" s="2">
@@ -24353,7 +24362,7 @@
         <v>75</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>81</v>
@@ -24373,10 +24382,10 @@
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -24452,7 +24461,7 @@
         <v>75</v>
       </c>
       <c r="AF218" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG218" t="s" s="2">
         <v>81</v>
@@ -24472,10 +24481,10 @@
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -24498,7 +24507,7 @@
         <v>75</v>
       </c>
       <c r="K219" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="L219" s="2"/>
       <c r="M219" s="2"/>
@@ -24551,7 +24560,7 @@
         <v>75</v>
       </c>
       <c r="AF219" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG219" t="s" s="2">
         <v>81</v>
@@ -24571,10 +24580,10 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -24597,7 +24606,7 @@
         <v>75</v>
       </c>
       <c r="K220" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="L220" s="2"/>
       <c r="M220" s="2"/>
@@ -24650,7 +24659,7 @@
         <v>75</v>
       </c>
       <c r="AF220" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG220" t="s" s="2">
         <v>81</v>
@@ -24670,10 +24679,10 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -24696,7 +24705,7 @@
         <v>75</v>
       </c>
       <c r="K221" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L221" s="2"/>
       <c r="M221" s="2"/>
@@ -24749,7 +24758,7 @@
         <v>75</v>
       </c>
       <c r="AF221" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG221" t="s" s="2">
         <v>81</v>
@@ -24769,10 +24778,10 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -24795,7 +24804,7 @@
         <v>75</v>
       </c>
       <c r="K222" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="L222" s="2"/>
       <c r="M222" s="2"/>
@@ -24848,7 +24857,7 @@
         <v>75</v>
       </c>
       <c r="AF222" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG222" t="s" s="2">
         <v>81</v>
@@ -24868,10 +24877,10 @@
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -24894,7 +24903,7 @@
         <v>75</v>
       </c>
       <c r="K223" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="L223" s="2"/>
       <c r="M223" s="2"/>
@@ -24947,7 +24956,7 @@
         <v>75</v>
       </c>
       <c r="AF223" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AG223" t="s" s="2">
         <v>81</v>
@@ -24967,10 +24976,10 @@
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -24993,7 +25002,7 @@
         <v>75</v>
       </c>
       <c r="K224" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="L224" s="2"/>
       <c r="M224" s="2"/>
@@ -25046,7 +25055,7 @@
         <v>75</v>
       </c>
       <c r="AF224" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AG224" t="s" s="2">
         <v>81</v>
@@ -25066,10 +25075,10 @@
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -25092,7 +25101,7 @@
         <v>75</v>
       </c>
       <c r="K225" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L225" s="2"/>
       <c r="M225" s="2"/>
@@ -25145,7 +25154,7 @@
         <v>75</v>
       </c>
       <c r="AF225" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AG225" t="s" s="2">
         <v>81</v>
@@ -25165,10 +25174,10 @@
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
@@ -25191,7 +25200,7 @@
         <v>75</v>
       </c>
       <c r="K226" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="L226" s="2"/>
       <c r="M226" s="2"/>
@@ -25244,7 +25253,7 @@
         <v>75</v>
       </c>
       <c r="AF226" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AG226" t="s" s="2">
         <v>81</v>
@@ -25264,10 +25273,10 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -25290,7 +25299,7 @@
         <v>75</v>
       </c>
       <c r="K227" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="L227" s="2"/>
       <c r="M227" s="2"/>
@@ -25343,7 +25352,7 @@
         <v>75</v>
       </c>
       <c r="AF227" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AG227" t="s" s="2">
         <v>81</v>
@@ -25363,10 +25372,10 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
@@ -25389,7 +25398,7 @@
         <v>75</v>
       </c>
       <c r="K228" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="L228" s="2"/>
       <c r="M228" s="2"/>
@@ -25442,7 +25451,7 @@
         <v>75</v>
       </c>
       <c r="AF228" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AG228" t="s" s="2">
         <v>81</v>
@@ -25462,10 +25471,10 @@
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
@@ -25488,7 +25497,7 @@
         <v>75</v>
       </c>
       <c r="K229" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="L229" s="2"/>
       <c r="M229" s="2"/>
@@ -25541,7 +25550,7 @@
         <v>75</v>
       </c>
       <c r="AF229" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AG229" t="s" s="2">
         <v>81</v>
@@ -25561,13 +25570,13 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C230" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D230" t="s" s="2">
         <v>75</v>
@@ -25589,7 +25598,7 @@
         <v>75</v>
       </c>
       <c r="K230" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="L230" s="2"/>
       <c r="M230" s="2"/>
@@ -25642,7 +25651,7 @@
         <v>75</v>
       </c>
       <c r="AF230" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG230" t="s" s="2">
         <v>81</v>
@@ -25662,10 +25671,10 @@
     </row>
     <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
@@ -25763,10 +25772,10 @@
     </row>
     <row r="232" hidden="true">
       <c r="A232" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
@@ -25864,10 +25873,10 @@
     </row>
     <row r="233" hidden="true">
       <c r="A233" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
@@ -25965,10 +25974,10 @@
     </row>
     <row r="234" hidden="true">
       <c r="A234" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
@@ -26066,10 +26075,10 @@
     </row>
     <row r="235" hidden="true">
       <c r="A235" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
@@ -26169,10 +26178,10 @@
     </row>
     <row r="236" hidden="true">
       <c r="A236" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
@@ -26272,10 +26281,10 @@
     </row>
     <row r="237" hidden="true">
       <c r="A237" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" t="s" s="2">
@@ -26375,10 +26384,10 @@
     </row>
     <row r="238" hidden="true">
       <c r="A238" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C238" s="2"/>
       <c r="D238" t="s" s="2">
@@ -26478,10 +26487,10 @@
     </row>
     <row r="239" hidden="true">
       <c r="A239" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" t="s" s="2">
@@ -26579,10 +26588,10 @@
     </row>
     <row r="240" hidden="true">
       <c r="A240" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" t="s" s="2">
@@ -26619,7 +26628,7 @@
         <v>75</v>
       </c>
       <c r="S240" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="T240" t="s" s="2">
         <v>75</v>
@@ -26638,7 +26647,7 @@
       </c>
       <c r="Y240" s="2"/>
       <c r="Z240" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AA240" t="s" s="2">
         <v>75</v>
@@ -26656,7 +26665,7 @@
         <v>75</v>
       </c>
       <c r="AF240" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG240" t="s" s="2">
         <v>76</v>
@@ -26676,10 +26685,10 @@
     </row>
     <row r="241" hidden="true">
       <c r="A241" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" t="s" s="2">
@@ -26706,7 +26715,7 @@
       </c>
       <c r="L241" s="2"/>
       <c r="M241" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N241" s="2"/>
       <c r="O241" s="2"/>
@@ -26757,7 +26766,7 @@
         <v>75</v>
       </c>
       <c r="AF241" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AG241" t="s" s="2">
         <v>81</v>
@@ -26777,10 +26786,10 @@
     </row>
     <row r="242" hidden="true">
       <c r="A242" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C242" s="2"/>
       <c r="D242" t="s" s="2">
@@ -26807,12 +26816,12 @@
       </c>
       <c r="L242" s="2"/>
       <c r="M242" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N242" s="2"/>
       <c r="O242" s="2"/>
       <c r="P242" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="Q242" s="2"/>
       <c r="R242" t="s" s="2">
@@ -26858,7 +26867,7 @@
         <v>75</v>
       </c>
       <c r="AF242" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG242" t="s" s="2">
         <v>81</v>
@@ -26878,10 +26887,10 @@
     </row>
     <row r="243" hidden="true">
       <c r="A243" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" t="s" s="2">
@@ -26957,7 +26966,7 @@
         <v>75</v>
       </c>
       <c r="AF243" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG243" t="s" s="2">
         <v>81</v>
@@ -26977,10 +26986,10 @@
     </row>
     <row r="244" hidden="true">
       <c r="A244" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C244" s="2"/>
       <c r="D244" t="s" s="2">
@@ -27003,7 +27012,7 @@
         <v>75</v>
       </c>
       <c r="K244" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="L244" s="2"/>
       <c r="M244" s="2"/>
@@ -27056,7 +27065,7 @@
         <v>75</v>
       </c>
       <c r="AF244" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG244" t="s" s="2">
         <v>81</v>
@@ -27076,10 +27085,10 @@
     </row>
     <row r="245" hidden="true">
       <c r="A245" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C245" s="2"/>
       <c r="D245" t="s" s="2">
@@ -27102,7 +27111,7 @@
         <v>75</v>
       </c>
       <c r="K245" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="L245" s="2"/>
       <c r="M245" s="2"/>
@@ -27155,7 +27164,7 @@
         <v>75</v>
       </c>
       <c r="AF245" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG245" t="s" s="2">
         <v>81</v>
@@ -27175,10 +27184,10 @@
     </row>
     <row r="246" hidden="true">
       <c r="A246" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C246" s="2"/>
       <c r="D246" t="s" s="2">
@@ -27201,7 +27210,7 @@
         <v>75</v>
       </c>
       <c r="K246" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L246" s="2"/>
       <c r="M246" s="2"/>
@@ -27254,7 +27263,7 @@
         <v>75</v>
       </c>
       <c r="AF246" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG246" t="s" s="2">
         <v>81</v>
@@ -27274,10 +27283,10 @@
     </row>
     <row r="247" hidden="true">
       <c r="A247" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C247" s="2"/>
       <c r="D247" t="s" s="2">
@@ -27300,7 +27309,7 @@
         <v>75</v>
       </c>
       <c r="K247" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="L247" s="2"/>
       <c r="M247" s="2"/>
@@ -27353,7 +27362,7 @@
         <v>75</v>
       </c>
       <c r="AF247" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG247" t="s" s="2">
         <v>81</v>
@@ -27373,10 +27382,10 @@
     </row>
     <row r="248" hidden="true">
       <c r="A248" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C248" s="2"/>
       <c r="D248" t="s" s="2">
@@ -27399,7 +27408,7 @@
         <v>75</v>
       </c>
       <c r="K248" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="L248" s="2"/>
       <c r="M248" s="2"/>
@@ -27452,7 +27461,7 @@
         <v>75</v>
       </c>
       <c r="AF248" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AG248" t="s" s="2">
         <v>81</v>
@@ -27472,10 +27481,10 @@
     </row>
     <row r="249" hidden="true">
       <c r="A249" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C249" s="2"/>
       <c r="D249" t="s" s="2">
@@ -27498,7 +27507,7 @@
         <v>75</v>
       </c>
       <c r="K249" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="L249" s="2"/>
       <c r="M249" s="2"/>
@@ -27551,7 +27560,7 @@
         <v>75</v>
       </c>
       <c r="AF249" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AG249" t="s" s="2">
         <v>81</v>
@@ -27571,10 +27580,10 @@
     </row>
     <row r="250" hidden="true">
       <c r="A250" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B250" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C250" s="2"/>
       <c r="D250" t="s" s="2">
@@ -27597,7 +27606,7 @@
         <v>75</v>
       </c>
       <c r="K250" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="L250" s="2"/>
       <c r="M250" s="2"/>
@@ -27650,7 +27659,7 @@
         <v>75</v>
       </c>
       <c r="AF250" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AG250" t="s" s="2">
         <v>81</v>
@@ -27670,10 +27679,10 @@
     </row>
     <row r="251" hidden="true">
       <c r="A251" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C251" s="2"/>
       <c r="D251" t="s" s="2">
@@ -27696,7 +27705,7 @@
         <v>75</v>
       </c>
       <c r="K251" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="L251" s="2"/>
       <c r="M251" s="2"/>
@@ -27749,7 +27758,7 @@
         <v>75</v>
       </c>
       <c r="AF251" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AG251" t="s" s="2">
         <v>81</v>
@@ -27769,10 +27778,10 @@
     </row>
     <row r="252" hidden="true">
       <c r="A252" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B252" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C252" s="2"/>
       <c r="D252" t="s" s="2">
@@ -27795,7 +27804,7 @@
         <v>75</v>
       </c>
       <c r="K252" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="L252" s="2"/>
       <c r="M252" s="2"/>
@@ -27848,7 +27857,7 @@
         <v>75</v>
       </c>
       <c r="AF252" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AG252" t="s" s="2">
         <v>81</v>
@@ -27868,10 +27877,10 @@
     </row>
     <row r="253" hidden="true">
       <c r="A253" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B253" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C253" s="2"/>
       <c r="D253" t="s" s="2">
@@ -27894,7 +27903,7 @@
         <v>75</v>
       </c>
       <c r="K253" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="L253" s="2"/>
       <c r="M253" s="2"/>
@@ -27947,7 +27956,7 @@
         <v>75</v>
       </c>
       <c r="AF253" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AG253" t="s" s="2">
         <v>81</v>
@@ -27967,10 +27976,10 @@
     </row>
     <row r="254" hidden="true">
       <c r="A254" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B254" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C254" s="2"/>
       <c r="D254" t="s" s="2">
@@ -27993,7 +28002,7 @@
         <v>75</v>
       </c>
       <c r="K254" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="L254" s="2"/>
       <c r="M254" s="2"/>
@@ -28046,7 +28055,7 @@
         <v>75</v>
       </c>
       <c r="AF254" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AG254" t="s" s="2">
         <v>81</v>
@@ -28066,13 +28075,13 @@
     </row>
     <row r="255" hidden="true">
       <c r="A255" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B255" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C255" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="D255" t="s" s="2">
         <v>75</v>
@@ -28094,7 +28103,7 @@
         <v>75</v>
       </c>
       <c r="K255" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="L255" s="2"/>
       <c r="M255" s="2"/>
@@ -28147,7 +28156,7 @@
         <v>75</v>
       </c>
       <c r="AF255" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG255" t="s" s="2">
         <v>81</v>
@@ -28167,10 +28176,10 @@
     </row>
     <row r="256" hidden="true">
       <c r="A256" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C256" s="2"/>
       <c r="D256" t="s" s="2">
@@ -28268,10 +28277,10 @@
     </row>
     <row r="257" hidden="true">
       <c r="A257" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C257" s="2"/>
       <c r="D257" t="s" s="2">
@@ -28369,10 +28378,10 @@
     </row>
     <row r="258" hidden="true">
       <c r="A258" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B258" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C258" s="2"/>
       <c r="D258" t="s" s="2">
@@ -28470,10 +28479,10 @@
     </row>
     <row r="259" hidden="true">
       <c r="A259" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B259" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C259" s="2"/>
       <c r="D259" t="s" s="2">
@@ -28571,10 +28580,10 @@
     </row>
     <row r="260" hidden="true">
       <c r="A260" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B260" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C260" s="2"/>
       <c r="D260" t="s" s="2">
@@ -28674,10 +28683,10 @@
     </row>
     <row r="261" hidden="true">
       <c r="A261" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B261" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C261" s="2"/>
       <c r="D261" t="s" s="2">
@@ -28777,10 +28786,10 @@
     </row>
     <row r="262" hidden="true">
       <c r="A262" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B262" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C262" s="2"/>
       <c r="D262" t="s" s="2">
@@ -28880,10 +28889,10 @@
     </row>
     <row r="263" hidden="true">
       <c r="A263" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B263" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C263" s="2"/>
       <c r="D263" t="s" s="2">
@@ -28983,10 +28992,10 @@
     </row>
     <row r="264" hidden="true">
       <c r="A264" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B264" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C264" s="2"/>
       <c r="D264" t="s" s="2">
@@ -29084,10 +29093,10 @@
     </row>
     <row r="265" hidden="true">
       <c r="A265" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B265" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C265" s="2"/>
       <c r="D265" t="s" s="2">
@@ -29124,7 +29133,7 @@
         <v>75</v>
       </c>
       <c r="S265" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="T265" t="s" s="2">
         <v>75</v>
@@ -29143,7 +29152,7 @@
       </c>
       <c r="Y265" s="2"/>
       <c r="Z265" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AA265" t="s" s="2">
         <v>75</v>
@@ -29161,7 +29170,7 @@
         <v>75</v>
       </c>
       <c r="AF265" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG265" t="s" s="2">
         <v>76</v>
@@ -29181,10 +29190,10 @@
     </row>
     <row r="266" hidden="true">
       <c r="A266" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B266" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C266" s="2"/>
       <c r="D266" t="s" s="2">
@@ -29211,7 +29220,7 @@
       </c>
       <c r="L266" s="2"/>
       <c r="M266" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N266" s="2"/>
       <c r="O266" s="2"/>
@@ -29262,7 +29271,7 @@
         <v>75</v>
       </c>
       <c r="AF266" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AG266" t="s" s="2">
         <v>81</v>
@@ -29282,10 +29291,10 @@
     </row>
     <row r="267" hidden="true">
       <c r="A267" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B267" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C267" s="2"/>
       <c r="D267" t="s" s="2">
@@ -29312,12 +29321,12 @@
       </c>
       <c r="L267" s="2"/>
       <c r="M267" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N267" s="2"/>
       <c r="O267" s="2"/>
       <c r="P267" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="Q267" s="2"/>
       <c r="R267" t="s" s="2">
@@ -29363,7 +29372,7 @@
         <v>75</v>
       </c>
       <c r="AF267" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG267" t="s" s="2">
         <v>81</v>
@@ -29383,10 +29392,10 @@
     </row>
     <row r="268" hidden="true">
       <c r="A268" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B268" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C268" s="2"/>
       <c r="D268" t="s" s="2">
@@ -29462,7 +29471,7 @@
         <v>75</v>
       </c>
       <c r="AF268" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG268" t="s" s="2">
         <v>81</v>
@@ -29482,10 +29491,10 @@
     </row>
     <row r="269" hidden="true">
       <c r="A269" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B269" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C269" s="2"/>
       <c r="D269" t="s" s="2">
@@ -29508,7 +29517,7 @@
         <v>75</v>
       </c>
       <c r="K269" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="L269" s="2"/>
       <c r="M269" s="2"/>
@@ -29561,7 +29570,7 @@
         <v>75</v>
       </c>
       <c r="AF269" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG269" t="s" s="2">
         <v>81</v>
@@ -29581,10 +29590,10 @@
     </row>
     <row r="270" hidden="true">
       <c r="A270" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B270" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C270" s="2"/>
       <c r="D270" t="s" s="2">
@@ -29607,7 +29616,7 @@
         <v>75</v>
       </c>
       <c r="K270" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="L270" s="2"/>
       <c r="M270" s="2"/>
@@ -29660,7 +29669,7 @@
         <v>75</v>
       </c>
       <c r="AF270" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG270" t="s" s="2">
         <v>81</v>
@@ -29680,10 +29689,10 @@
     </row>
     <row r="271" hidden="true">
       <c r="A271" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B271" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C271" s="2"/>
       <c r="D271" t="s" s="2">
@@ -29706,7 +29715,7 @@
         <v>75</v>
       </c>
       <c r="K271" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="L271" s="2"/>
       <c r="M271" s="2"/>
@@ -29759,7 +29768,7 @@
         <v>75</v>
       </c>
       <c r="AF271" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG271" t="s" s="2">
         <v>81</v>
@@ -29779,10 +29788,10 @@
     </row>
     <row r="272" hidden="true">
       <c r="A272" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B272" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C272" s="2"/>
       <c r="D272" t="s" s="2">
@@ -29805,7 +29814,7 @@
         <v>75</v>
       </c>
       <c r="K272" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="L272" s="2"/>
       <c r="M272" s="2"/>
@@ -29858,7 +29867,7 @@
         <v>75</v>
       </c>
       <c r="AF272" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG272" t="s" s="2">
         <v>81</v>
@@ -29878,10 +29887,10 @@
     </row>
     <row r="273" hidden="true">
       <c r="A273" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B273" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C273" s="2"/>
       <c r="D273" t="s" s="2">
@@ -29904,7 +29913,7 @@
         <v>75</v>
       </c>
       <c r="K273" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="L273" s="2"/>
       <c r="M273" s="2"/>
@@ -29957,7 +29966,7 @@
         <v>75</v>
       </c>
       <c r="AF273" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AG273" t="s" s="2">
         <v>81</v>
@@ -29977,10 +29986,10 @@
     </row>
     <row r="274" hidden="true">
       <c r="A274" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B274" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C274" s="2"/>
       <c r="D274" t="s" s="2">
@@ -30003,7 +30012,7 @@
         <v>75</v>
       </c>
       <c r="K274" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="L274" s="2"/>
       <c r="M274" s="2"/>
@@ -30056,7 +30065,7 @@
         <v>75</v>
       </c>
       <c r="AF274" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AG274" t="s" s="2">
         <v>81</v>
@@ -30076,10 +30085,10 @@
     </row>
     <row r="275" hidden="true">
       <c r="A275" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B275" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C275" s="2"/>
       <c r="D275" t="s" s="2">
@@ -30102,7 +30111,7 @@
         <v>75</v>
       </c>
       <c r="K275" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="L275" s="2"/>
       <c r="M275" s="2"/>
@@ -30155,7 +30164,7 @@
         <v>75</v>
       </c>
       <c r="AF275" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AG275" t="s" s="2">
         <v>81</v>
@@ -30175,10 +30184,10 @@
     </row>
     <row r="276" hidden="true">
       <c r="A276" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B276" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C276" s="2"/>
       <c r="D276" t="s" s="2">
@@ -30201,7 +30210,7 @@
         <v>75</v>
       </c>
       <c r="K276" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="L276" s="2"/>
       <c r="M276" s="2"/>
@@ -30254,7 +30263,7 @@
         <v>75</v>
       </c>
       <c r="AF276" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AG276" t="s" s="2">
         <v>81</v>
@@ -30274,10 +30283,10 @@
     </row>
     <row r="277" hidden="true">
       <c r="A277" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B277" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C277" s="2"/>
       <c r="D277" t="s" s="2">
@@ -30300,7 +30309,7 @@
         <v>75</v>
       </c>
       <c r="K277" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="L277" s="2"/>
       <c r="M277" s="2"/>
@@ -30353,7 +30362,7 @@
         <v>75</v>
       </c>
       <c r="AF277" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AG277" t="s" s="2">
         <v>81</v>
@@ -30373,10 +30382,10 @@
     </row>
     <row r="278" hidden="true">
       <c r="A278" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B278" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C278" s="2"/>
       <c r="D278" t="s" s="2">
@@ -30399,7 +30408,7 @@
         <v>75</v>
       </c>
       <c r="K278" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="L278" s="2"/>
       <c r="M278" s="2"/>
@@ -30452,7 +30461,7 @@
         <v>75</v>
       </c>
       <c r="AF278" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AG278" t="s" s="2">
         <v>81</v>
@@ -30472,10 +30481,10 @@
     </row>
     <row r="279" hidden="true">
       <c r="A279" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B279" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C279" s="2"/>
       <c r="D279" t="s" s="2">
@@ -30498,7 +30507,7 @@
         <v>75</v>
       </c>
       <c r="K279" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="L279" s="2"/>
       <c r="M279" s="2"/>
@@ -30551,7 +30560,7 @@
         <v>75</v>
       </c>
       <c r="AF279" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AG279" t="s" s="2">
         <v>81</v>
@@ -30571,13 +30580,13 @@
     </row>
     <row r="280" hidden="true">
       <c r="A280" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B280" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C280" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="D280" t="s" s="2">
         <v>75</v>
@@ -30599,7 +30608,7 @@
         <v>75</v>
       </c>
       <c r="K280" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="L280" s="2"/>
       <c r="M280" s="2"/>
@@ -30652,7 +30661,7 @@
         <v>75</v>
       </c>
       <c r="AF280" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG280" t="s" s="2">
         <v>81</v>
@@ -30672,10 +30681,10 @@
     </row>
     <row r="281" hidden="true">
       <c r="A281" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B281" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C281" s="2"/>
       <c r="D281" t="s" s="2">
@@ -30773,10 +30782,10 @@
     </row>
     <row r="282" hidden="true">
       <c r="A282" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B282" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C282" s="2"/>
       <c r="D282" t="s" s="2">
@@ -30874,10 +30883,10 @@
     </row>
     <row r="283" hidden="true">
       <c r="A283" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B283" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C283" s="2"/>
       <c r="D283" t="s" s="2">
@@ -30975,10 +30984,10 @@
     </row>
     <row r="284" hidden="true">
       <c r="A284" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B284" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C284" s="2"/>
       <c r="D284" t="s" s="2">
@@ -31076,10 +31085,10 @@
     </row>
     <row r="285" hidden="true">
       <c r="A285" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B285" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C285" s="2"/>
       <c r="D285" t="s" s="2">
@@ -31179,10 +31188,10 @@
     </row>
     <row r="286" hidden="true">
       <c r="A286" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B286" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C286" s="2"/>
       <c r="D286" t="s" s="2">
@@ -31282,10 +31291,10 @@
     </row>
     <row r="287" hidden="true">
       <c r="A287" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B287" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C287" s="2"/>
       <c r="D287" t="s" s="2">
@@ -31385,10 +31394,10 @@
     </row>
     <row r="288" hidden="true">
       <c r="A288" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B288" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C288" s="2"/>
       <c r="D288" t="s" s="2">
@@ -31488,10 +31497,10 @@
     </row>
     <row r="289" hidden="true">
       <c r="A289" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B289" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C289" s="2"/>
       <c r="D289" t="s" s="2">
@@ -31589,10 +31598,10 @@
     </row>
     <row r="290" hidden="true">
       <c r="A290" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B290" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C290" s="2"/>
       <c r="D290" t="s" s="2">
@@ -31629,7 +31638,7 @@
         <v>75</v>
       </c>
       <c r="S290" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="T290" t="s" s="2">
         <v>75</v>
@@ -31648,7 +31657,7 @@
       </c>
       <c r="Y290" s="2"/>
       <c r="Z290" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AA290" t="s" s="2">
         <v>75</v>
@@ -31666,7 +31675,7 @@
         <v>75</v>
       </c>
       <c r="AF290" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG290" t="s" s="2">
         <v>76</v>
@@ -31686,10 +31695,10 @@
     </row>
     <row r="291" hidden="true">
       <c r="A291" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B291" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C291" s="2"/>
       <c r="D291" t="s" s="2">
@@ -31716,7 +31725,7 @@
       </c>
       <c r="L291" s="2"/>
       <c r="M291" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N291" s="2"/>
       <c r="O291" s="2"/>
@@ -31767,7 +31776,7 @@
         <v>75</v>
       </c>
       <c r="AF291" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AG291" t="s" s="2">
         <v>81</v>
@@ -31787,10 +31796,10 @@
     </row>
     <row r="292" hidden="true">
       <c r="A292" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B292" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C292" s="2"/>
       <c r="D292" t="s" s="2">
@@ -31817,12 +31826,12 @@
       </c>
       <c r="L292" s="2"/>
       <c r="M292" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N292" s="2"/>
       <c r="O292" s="2"/>
       <c r="P292" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="Q292" s="2"/>
       <c r="R292" t="s" s="2">
@@ -31868,7 +31877,7 @@
         <v>75</v>
       </c>
       <c r="AF292" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG292" t="s" s="2">
         <v>81</v>
@@ -31888,10 +31897,10 @@
     </row>
     <row r="293" hidden="true">
       <c r="A293" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B293" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C293" s="2"/>
       <c r="D293" t="s" s="2">
@@ -31967,7 +31976,7 @@
         <v>75</v>
       </c>
       <c r="AF293" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG293" t="s" s="2">
         <v>81</v>
@@ -31987,10 +31996,10 @@
     </row>
     <row r="294" hidden="true">
       <c r="A294" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B294" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C294" s="2"/>
       <c r="D294" t="s" s="2">
@@ -32013,7 +32022,7 @@
         <v>75</v>
       </c>
       <c r="K294" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="L294" s="2"/>
       <c r="M294" s="2"/>
@@ -32066,7 +32075,7 @@
         <v>75</v>
       </c>
       <c r="AF294" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG294" t="s" s="2">
         <v>81</v>
@@ -32086,10 +32095,10 @@
     </row>
     <row r="295" hidden="true">
       <c r="A295" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B295" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C295" s="2"/>
       <c r="D295" t="s" s="2">
@@ -32112,7 +32121,7 @@
         <v>75</v>
       </c>
       <c r="K295" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="L295" s="2"/>
       <c r="M295" s="2"/>
@@ -32165,7 +32174,7 @@
         <v>75</v>
       </c>
       <c r="AF295" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG295" t="s" s="2">
         <v>81</v>
@@ -32185,10 +32194,10 @@
     </row>
     <row r="296" hidden="true">
       <c r="A296" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B296" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C296" s="2"/>
       <c r="D296" t="s" s="2">
@@ -32211,7 +32220,7 @@
         <v>75</v>
       </c>
       <c r="K296" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L296" s="2"/>
       <c r="M296" s="2"/>
@@ -32264,7 +32273,7 @@
         <v>75</v>
       </c>
       <c r="AF296" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG296" t="s" s="2">
         <v>81</v>
@@ -32284,10 +32293,10 @@
     </row>
     <row r="297" hidden="true">
       <c r="A297" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B297" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C297" s="2"/>
       <c r="D297" t="s" s="2">
@@ -32310,7 +32319,7 @@
         <v>75</v>
       </c>
       <c r="K297" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="L297" s="2"/>
       <c r="M297" s="2"/>
@@ -32363,7 +32372,7 @@
         <v>75</v>
       </c>
       <c r="AF297" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG297" t="s" s="2">
         <v>81</v>
@@ -32383,10 +32392,10 @@
     </row>
     <row r="298" hidden="true">
       <c r="A298" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B298" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C298" s="2"/>
       <c r="D298" t="s" s="2">
@@ -32409,7 +32418,7 @@
         <v>75</v>
       </c>
       <c r="K298" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="L298" s="2"/>
       <c r="M298" s="2"/>
@@ -32462,7 +32471,7 @@
         <v>75</v>
       </c>
       <c r="AF298" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AG298" t="s" s="2">
         <v>81</v>
@@ -32482,10 +32491,10 @@
     </row>
     <row r="299" hidden="true">
       <c r="A299" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B299" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C299" s="2"/>
       <c r="D299" t="s" s="2">
@@ -32508,7 +32517,7 @@
         <v>75</v>
       </c>
       <c r="K299" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="L299" s="2"/>
       <c r="M299" s="2"/>
@@ -32561,7 +32570,7 @@
         <v>75</v>
       </c>
       <c r="AF299" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AG299" t="s" s="2">
         <v>81</v>
@@ -32581,10 +32590,10 @@
     </row>
     <row r="300" hidden="true">
       <c r="A300" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B300" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C300" s="2"/>
       <c r="D300" t="s" s="2">
@@ -32607,7 +32616,7 @@
         <v>75</v>
       </c>
       <c r="K300" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="L300" s="2"/>
       <c r="M300" s="2"/>
@@ -32660,7 +32669,7 @@
         <v>75</v>
       </c>
       <c r="AF300" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AG300" t="s" s="2">
         <v>81</v>
@@ -32680,10 +32689,10 @@
     </row>
     <row r="301" hidden="true">
       <c r="A301" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B301" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C301" s="2"/>
       <c r="D301" t="s" s="2">
@@ -32706,7 +32715,7 @@
         <v>75</v>
       </c>
       <c r="K301" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="L301" s="2"/>
       <c r="M301" s="2"/>
@@ -32759,7 +32768,7 @@
         <v>75</v>
       </c>
       <c r="AF301" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AG301" t="s" s="2">
         <v>81</v>
@@ -32779,10 +32788,10 @@
     </row>
     <row r="302" hidden="true">
       <c r="A302" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B302" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C302" s="2"/>
       <c r="D302" t="s" s="2">
@@ -32805,7 +32814,7 @@
         <v>75</v>
       </c>
       <c r="K302" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="L302" s="2"/>
       <c r="M302" s="2"/>
@@ -32858,7 +32867,7 @@
         <v>75</v>
       </c>
       <c r="AF302" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AG302" t="s" s="2">
         <v>81</v>
@@ -32878,10 +32887,10 @@
     </row>
     <row r="303" hidden="true">
       <c r="A303" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B303" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C303" s="2"/>
       <c r="D303" t="s" s="2">
@@ -32904,7 +32913,7 @@
         <v>75</v>
       </c>
       <c r="K303" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="L303" s="2"/>
       <c r="M303" s="2"/>
@@ -32957,7 +32966,7 @@
         <v>75</v>
       </c>
       <c r="AF303" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AG303" t="s" s="2">
         <v>81</v>
@@ -32977,10 +32986,10 @@
     </row>
     <row r="304" hidden="true">
       <c r="A304" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B304" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C304" s="2"/>
       <c r="D304" t="s" s="2">
@@ -33003,7 +33012,7 @@
         <v>75</v>
       </c>
       <c r="K304" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="L304" s="2"/>
       <c r="M304" s="2"/>
@@ -33056,7 +33065,7 @@
         <v>75</v>
       </c>
       <c r="AF304" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AG304" t="s" s="2">
         <v>81</v>
@@ -33076,10 +33085,10 @@
     </row>
     <row r="305" hidden="true">
       <c r="A305" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B305" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C305" s="2"/>
       <c r="D305" t="s" s="2">
@@ -33102,7 +33111,7 @@
         <v>75</v>
       </c>
       <c r="K305" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="L305" s="2"/>
       <c r="M305" s="2"/>
@@ -33155,7 +33164,7 @@
         <v>75</v>
       </c>
       <c r="AF305" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="AG305" t="s" s="2">
         <v>81</v>
@@ -33175,10 +33184,10 @@
     </row>
     <row r="306" hidden="true">
       <c r="A306" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B306" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C306" s="2"/>
       <c r="D306" t="s" s="2">
@@ -33201,7 +33210,7 @@
         <v>75</v>
       </c>
       <c r="K306" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="L306" s="2"/>
       <c r="M306" s="2"/>
@@ -33254,7 +33263,7 @@
         <v>75</v>
       </c>
       <c r="AF306" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AG306" t="s" s="2">
         <v>81</v>
@@ -33274,10 +33283,10 @@
     </row>
     <row r="307" hidden="true">
       <c r="A307" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B307" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C307" s="2"/>
       <c r="D307" t="s" s="2">
@@ -33300,7 +33309,7 @@
         <v>75</v>
       </c>
       <c r="K307" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="L307" s="2"/>
       <c r="M307" s="2"/>
@@ -33353,7 +33362,7 @@
         <v>75</v>
       </c>
       <c r="AF307" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AG307" t="s" s="2">
         <v>81</v>
@@ -33373,10 +33382,10 @@
     </row>
     <row r="308" hidden="true">
       <c r="A308" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B308" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C308" s="2"/>
       <c r="D308" t="s" s="2">
@@ -33399,7 +33408,7 @@
         <v>75</v>
       </c>
       <c r="K308" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="L308" s="2"/>
       <c r="M308" s="2"/>
@@ -33452,7 +33461,7 @@
         <v>75</v>
       </c>
       <c r="AF308" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AG308" t="s" s="2">
         <v>81</v>

--- a/fix/slicing-type-this/ig/StructureDefinition-fr-cda-resultats-examens-de-biologie-medicale.xlsx
+++ b/fix/slicing-type-this/ig/StructureDefinition-fr-cda-resultats-examens-de-biologie-medicale.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T10:07:19+00:00</t>
+    <t>2026-10-08T14:58:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/slicing-type-this/ig/StructureDefinition-fr-cda-resultats-examens-de-biologie-medicale.xlsx
+++ b/fix/slicing-type-this/ig/StructureDefinition-fr-cda-resultats-examens-de-biologie-medicale.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T14:58:47+00:00</t>
+    <t>2026-10-12T13:25:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/slicing-type-this/ig/StructureDefinition-fr-cda-resultats-examens-de-biologie-medicale.xlsx
+++ b/fix/slicing-type-this/ig/StructureDefinition-fr-cda-resultats-examens-de-biologie-medicale.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T13:25:25+00:00</t>
+    <t>2026-10-14T12:53:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
